--- a/s01/S01_ALU_02_Instrumento_Expediente.xlsx
+++ b/s01/S01_ALU_02_Instrumento_Expediente.xlsx
@@ -10,9 +10,10 @@
   <sheets>
     <sheet name="Cómo se usa" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Instrumento" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Casos difíciles" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Trazabilidad" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Mi brecha" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Comparativo por anexo" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Casos difíciles" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Trazabilidad" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Mi brecha" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Instrumento!$A$5:$I$116</definedName>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="437">
   <si>
     <t xml:space="preserve">INSTRUMENTO DE EXPEDIENTE DE IDENTIFICACIÓN</t>
   </si>
@@ -881,6 +882,186 @@
     <t xml:space="preserve">Acta constitutiva · carpeta \Clientes\ACME\01_identificacion</t>
   </si>
   <si>
+    <t xml:space="preserve">QUÉ PIDE CADA ANEXO — MATRIZ COMPARATIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada anexo redacta y numera distinto los mismos conceptos. Aquí están normalizados: hacia abajo el requisito, a la derecha el anexo, y en la celda el numeral exacto donde vive. Una celda vacía significa que ese anexo no lo pide.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 3
+Persona física mexicana o residente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 4
+Persona moral mexicana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 4 Bis
+Persona moral de derecho público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 5
+Persona física extranjera (visitante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 6
+Persona moral extranjera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 6 Bis
+Embajada, consulado, organismo int.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 7
+Simplificado (Anexo 7-A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 7 Bis
+Simplificado de derecho público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEXO 8
+Fideicomiso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre, denominación o razón social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a) i) del fiduciario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de nacimiento, constitución o creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a) ii) o RFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a) iii) o RFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">País de nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">País de nacionalidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actividad, ocupación u objeto social — sólo si hay Relación de negocios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domicilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teléfono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correo electrónico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURP y RFC (o número de identificación fiscal extranjero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datos de la identificación con la que se identificó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domicilio en México cuando reside en el extranjero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a) párr. final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número, referencia o identificador del fideicomiso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datos del representante, apoderado, funcionario o delegado fiduciario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificación oficial vigente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b) i) pasaporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento migratorio del INM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constancia de CURP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprobante de domicilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constancia de domicilio en ciertas fracciones del art. 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b) iii) párr. 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumento de constitución o documento de existencia legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cédula de Identificación Fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poderes del representante o apoderado, y su identificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b) v) carta poder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b) iv) CONSTANCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b) v) IDENTIFICAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEROGADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b) iv) IDENTIFICAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceptos que pide este anexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÓMO SE LEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El numeral (por ejemplo «a) iii)»)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ese anexo sí lo pide, y ése es su numeral exacto dentro del anexo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una raya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ese anexo no pide ese concepto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDENTIFICAR — verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anexos 4, 6 y 8. Ya no basta la declaración del cliente: hay que identificar al Beneficiario Controlador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSTANCIA — ámbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anexos 3 y 5. Se conserva la constancia declarativa firmada por el cliente, ahora también con Firma Electrónica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEROGADA — rojo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anexo 6 Bis. Se eliminó la constancia para embajadas, consulados y organismos internacionales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente: ACUERDO 115/2026, DOF 7 de agosto de 2026 · Anexos 3 a 8 de las Reglas de Carácter General. Los conceptos fueron normalizados por GMC360 porque cada anexo los redacta y numera distinto; el numeral de cada celda sí es literal. El único texto con valor legal es el publicado en el DOF.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LOS OCHO CASOS QUE ROMPEN EL EXPEDIENTE</t>
   </si>
   <si>
@@ -905,10 +1086,12 @@
     <t xml:space="preserve">El cliente se niega a darte la información o los documentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Te abstienes de llevar a cabo el acto u operación, «sin responsabilidad alguna». No es que puedas negarte: es que debes, y la Ley te cubre. Deja constancia escrita de la negativa y de la fecha.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L 21</t>
+    <t xml:space="preserve">PRIMERO: te abstienes de llevar a cabo el acto u operación, «sin responsabilidad alguna» (L 21). No es que puedas negarte: es que debes, y la Ley te cubre. Deja constancia escrita de la negativa y de la fecha.
+Y ADEMÁS, si de esa negativa nace sospecha sobre el origen o destino de los recursos, hay aviso de 24 horas — aunque no haya contrato y aunque sólo cuentes con los datos de quien INTENTÓ la operación (L 18 fr. VI, que dice «incluso si el acto u operación no se celebró», y R 7 Bis).
+OJO CON EL LÍMITE: negarse a dar papeles no es lo mismo que sospechar del origen del dinero. Confundirlos genera avisos basura. La pregunta correcta es por qué se negó, y si eso te hace sospechar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L 21 · L 18 fr. VI · R 7 Bis</t>
   </si>
   <si>
     <t xml:space="preserve">El documento de identificación trae tachaduras o enmendaduras</t>
@@ -1178,7 +1361,7 @@
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1345,8 +1528,63 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="9.5"/>
-      <color rgb="FF5A6472"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF12224A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFC5CBD6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8.5"/>
+      <color rgb="FFC4622B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8.5"/>
+      <color rgb="FF1B5E3F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8.5"/>
+      <color rgb="FFB3261E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FF12224A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1355,6 +1593,13 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF12224A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF5A6472"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1384,7 +1629,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1413,6 +1658,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1E2761"/>
         <bgColor rgb="FF12224A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F2EB"/>
+        <bgColor rgb="FFE2E7F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEEEC"/>
+        <bgColor rgb="FFFDF3E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F6FA"/>
+        <bgColor rgb="FFFBEEEC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1465,7 +1728,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1582,6 +1845,70 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1598,7 +1925,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1618,11 +1945,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1630,19 +1957,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1868,7 +2191,7 @@
       <rgbColor rgb="FF8A5A12"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAAB2BF"/>
+      <rgbColor rgb="FFC5CBD6"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -1901,7 +2224,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFC4622B"/>
       <rgbColor rgb="FF5A6472"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFAAB2BF"/>
       <rgbColor rgb="FF12224A"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF16202E"/>
@@ -5100,6 +5423,1024 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="1" width="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+    </row>
+    <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="K7" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L12" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K15" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L15" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K16" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L16" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K17" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K19" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L19" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K20" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L20" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K21" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L21" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K22" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L22" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K23" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L23" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="31" t="s">
+        <v>320</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K24" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L24" s="33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="J25" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L25" s="33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="J26" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K26" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>326</v>
+      </c>
+      <c r="J27" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K27" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="L27" s="38" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="40" t="s">
+        <v>328</v>
+      </c>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42" t="n">
+        <f aca="false">COUNTIFS(D6:D27,"&lt;&gt;—",D6:D27,"&lt;&gt;DEROGADA")</f>
+        <v>16</v>
+      </c>
+      <c r="E28" s="42" t="n">
+        <f aca="false">COUNTIFS(E6:E27,"&lt;&gt;—",E6:E27,"&lt;&gt;DEROGADA")</f>
+        <v>14</v>
+      </c>
+      <c r="F28" s="42" t="n">
+        <f aca="false">COUNTIFS(F6:F27,"&lt;&gt;—",F6:F27,"&lt;&gt;DEROGADA")</f>
+        <v>11</v>
+      </c>
+      <c r="G28" s="42" t="n">
+        <f aca="false">COUNTIFS(G6:G27,"&lt;&gt;—",G6:G27,"&lt;&gt;DEROGADA")</f>
+        <v>14</v>
+      </c>
+      <c r="H28" s="42" t="n">
+        <f aca="false">COUNTIFS(H6:H27,"&lt;&gt;—",H6:H27,"&lt;&gt;DEROGADA")</f>
+        <v>14</v>
+      </c>
+      <c r="I28" s="42" t="n">
+        <f aca="false">COUNTIFS(I6:I27,"&lt;&gt;—",I6:I27,"&lt;&gt;DEROGADA")</f>
+        <v>11</v>
+      </c>
+      <c r="J28" s="42" t="n">
+        <f aca="false">COUNTIFS(J6:J27,"&lt;&gt;—",J6:J27,"&lt;&gt;DEROGADA")</f>
+        <v>8</v>
+      </c>
+      <c r="K28" s="42" t="n">
+        <f aca="false">COUNTIFS(K6:K27,"&lt;&gt;—",K6:K27,"&lt;&gt;DEROGADA")</f>
+        <v>5</v>
+      </c>
+      <c r="L28" s="42" t="n">
+        <f aca="false">COUNTIFS(L6:L27,"&lt;&gt;—",L6:L27,"&lt;&gt;DEROGADA")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>331</v>
+      </c>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+    </row>
+    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+    </row>
+    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>335</v>
+      </c>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>339</v>
+      </c>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="B37:L37"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -5113,7 +6454,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5123,7 +6464,7 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -5133,167 +6474,167 @@
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>293</v>
+      <c r="B6" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>350</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>296</v>
+      <c r="B7" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>353</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>299</v>
+      <c r="B8" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>355</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>356</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>300</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>302</v>
+      <c r="B9" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>358</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>359</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29" t="n">
+      <c r="A10" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>305</v>
+      <c r="B10" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>361</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>362</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29" t="n">
+      <c r="A11" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>308</v>
+      <c r="B11" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>364</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>365</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>311</v>
+      <c r="B12" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>367</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>368</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="n">
+      <c r="A13" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>314</v>
+      <c r="B13" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>370</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>371</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>315</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33" t="s">
-        <v>316</v>
-      </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
+      <c r="B16" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="34" t="s">
-        <v>317</v>
+      <c r="B18" s="50" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5323,7 +6664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5341,7 +6682,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5351,7 +6692,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>319</v>
+        <v>376</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -5361,36 +6702,36 @@
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>320</v>
+        <v>377</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>321</v>
+        <v>378</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>322</v>
+        <v>379</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>323</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>324</v>
+      <c r="B6" s="51" t="s">
+        <v>381</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="24"/>
@@ -5399,14 +6740,14 @@
       <c r="A7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="35" t="s">
-        <v>327</v>
+      <c r="B7" s="51" t="s">
+        <v>384</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="24"/>
@@ -5415,14 +6756,14 @@
       <c r="A8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>330</v>
+      <c r="B8" s="51" t="s">
+        <v>387</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="24"/>
@@ -5431,14 +6772,14 @@
       <c r="A9" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>333</v>
+      <c r="B9" s="51" t="s">
+        <v>390</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
@@ -5447,14 +6788,14 @@
       <c r="A10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>336</v>
+      <c r="B10" s="51" t="s">
+        <v>393</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -5463,14 +6804,14 @@
       <c r="A11" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>339</v>
+      <c r="B11" s="51" t="s">
+        <v>396</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="24"/>
@@ -5479,14 +6820,14 @@
       <c r="A12" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>342</v>
+      <c r="B12" s="51" t="s">
+        <v>399</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>344</v>
+        <v>401</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="24"/>
@@ -5495,14 +6836,14 @@
       <c r="A13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>345</v>
+      <c r="B13" s="51" t="s">
+        <v>402</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>346</v>
+        <v>403</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="24"/>
@@ -5511,29 +6852,29 @@
       <c r="A14" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="35" t="s">
-        <v>348</v>
+      <c r="B14" s="51" t="s">
+        <v>405</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="14" t="s">
-        <v>351</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="36" t="s">
-        <v>352</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
+      <c r="B17" s="52" t="s">
+        <v>409</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5568,7 +6909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5584,7 +6925,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5592,227 +6933,227 @@
       <c r="E1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
+      <c r="B3" s="53" t="s">
+        <v>411</v>
+      </c>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="39" t="n">
+      <c r="B6" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="55" t="n">
         <f aca="false">COUNTIF(Instrumento!$B$6:$B$116,"Sí")</f>
         <v>20</v>
       </c>
-      <c r="E6" s="40" t="s">
-        <v>357</v>
+      <c r="E6" s="56" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="41" t="s">
-        <v>358</v>
-      </c>
-      <c r="C7" s="42" t="n">
+      <c r="B7" s="31" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="57" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$H$6:$H$116,"No aplica")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>359</v>
+      <c r="E7" s="56" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="41" t="s">
-        <v>360</v>
-      </c>
-      <c r="C8" s="42" t="n">
+      <c r="B8" s="31" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" s="57" t="n">
         <f aca="false">C6-C7</f>
         <v>20</v>
       </c>
-      <c r="E8" s="40" t="s">
-        <v>361</v>
+      <c r="E8" s="56" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41" t="s">
-        <v>362</v>
-      </c>
-      <c r="C9" s="42" t="n">
+      <c r="B9" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="C9" s="57" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$H$6:$H$116,"Sí")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="40"/>
+      <c r="E9" s="56"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="C10" s="42" t="n">
+      <c r="B10" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="57" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$H$6:$H$116,"Parcial")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="40" t="s">
-        <v>364</v>
+      <c r="E10" s="56" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="41" t="s">
-        <v>365</v>
-      </c>
-      <c r="C11" s="42" t="n">
+      <c r="B11" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="57" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$H$6:$H$116,"No")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="40" t="s">
-        <v>366</v>
+      <c r="E11" s="56" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="41" t="s">
-        <v>367</v>
-      </c>
-      <c r="C12" s="42" t="n">
+      <c r="B12" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="C12" s="57" t="n">
         <f aca="false">C8-C9-C10-C11</f>
         <v>20</v>
       </c>
-      <c r="E12" s="40" t="s">
-        <v>368</v>
+      <c r="E12" s="56" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="C14" s="43" t="n">
+      <c r="B14" s="54" t="s">
+        <v>426</v>
+      </c>
+      <c r="C14" s="58" t="n">
         <f aca="false">IF(C8=0,0,(C9+C10*0.5)/C8)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="40" t="s">
-        <v>370</v>
+      <c r="E14" s="56" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="44" t="str">
+      <c r="B16" s="59" t="str">
         <f aca="false">IF(C12&gt;0,"Contesta primero los "&amp;C12&amp;" renglones que faltan",IF(C14&gt;=0.9,"VERDE · expediente defendible. Falta poco.",IF(C14&gt;=0.6,"ÁMBAR · el expediente existe pero tiene huecos. Ciérralos antes del 30 de noviembre.","ROJO · el expediente no resiste una verificación. Es tu primer proyecto, antes del manual.")))</f>
         <v>Contesta primero los 20 renglones que faltan</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="45" t="s">
-        <v>372</v>
-      </c>
-      <c r="D19" s="45" t="s">
-        <v>373</v>
-      </c>
-      <c r="E19" s="45" t="s">
-        <v>374</v>
+      <c r="C19" s="60" t="s">
+        <v>429</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="60" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="47" t="n">
+      <c r="B20" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="62" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$D$6:$D$116,"Dato")</f>
         <v>13</v>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="62" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$D$6:$D$116,"Dato",Instrumento!$H$6:$H$116,"Sí")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="48" t="n">
+      <c r="E20" s="63" t="n">
         <f aca="false">IF(C20=0,"—",D20/C20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="47" t="n">
+      <c r="C21" s="62" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$D$6:$D$116,"Documento")</f>
         <v>6</v>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="62" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$D$6:$D$116,"Documento",Instrumento!$H$6:$H$116,"Sí")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="48" t="n">
+      <c r="E21" s="63" t="n">
         <f aca="false">IF(C21=0,"—",D21/C21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="47" t="n">
+      <c r="C22" s="62" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$D$6:$D$116,"Constancia")</f>
         <v>1</v>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="62" t="n">
         <f aca="false">COUNTIFS(Instrumento!$B$6:$B$116,"Sí",Instrumento!$D$6:$D$116,"Constancia",Instrumento!$H$6:$H$116,"Sí")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="48" t="n">
+      <c r="E22" s="63" t="n">
         <f aca="false">IF(C22=0,"—",D22/C22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="49" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
+      <c r="B25" s="64" t="s">
+        <v>433</v>
+      </c>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="49" t="s">
-        <v>377</v>
-      </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
+      <c r="B26" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="49" t="s">
-        <v>378</v>
-      </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
+      <c r="B27" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="49" t="s">
-        <v>379</v>
-      </c>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
+      <c r="B28" s="64" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5844,7 +7185,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70A82648-8020-43B8-959F-66B043BD8359}</x14:id>
+          <x14:id>{87E21DD0-FB98-4FE7-A737-E0B77D804035}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5860,7 +7201,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70A82648-8020-43B8-959F-66B043BD8359}">
+          <x14:cfRule type="dataBar" id="{87E21DD0-FB98-4FE7-A737-E0B77D804035}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/s01/S01_ALU_02_Instrumento_Expediente.xlsx
+++ b/s01/S01_ALU_02_Instrumento_Expediente.xlsx
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">Resguardo</t>
   </si>
   <si>
-    <t xml:space="preserve">Todo lo anterior, físico o electrónico, en el domicilio registrado ante la Secretaría, por al menos diez años desde la realización de la Actividad Vulnerable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L 18, párrafo posterior a las fracciones — excepto la fracción XIV del artículo 17</t>
+    <t xml:space="preserve">Todo lo anterior, físico o electrónico, por al menos diez años contados desde la realización de la Actividad Vulnerable. Se conserva en el domicilio registrado ante la Secretaría, salvo la fracción XIV del artículo 17: esa fracción está exceptuada del domicilio, no del plazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L 18 fr. IV, segundo párrafo</t>
   </si>
   <si>
     <t xml:space="preserve">Dos eslabones no son norma y están marcados como tales.</t>
@@ -1733,259 +1733,259 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="31" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7185,7 +7185,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87E21DD0-FB98-4FE7-A737-E0B77D804035}</x14:id>
+          <x14:id>{D32AE212-FE10-4CF0-90EC-3D48F4509875}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7201,7 +7201,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{87E21DD0-FB98-4FE7-A737-E0B77D804035}">
+          <x14:cfRule type="dataBar" id="{D32AE212-FE10-4CF0-90EC-3D48F4509875}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
